--- a/public/tamplate_excel/corp.xlsx
+++ b/public/tamplate_excel/corp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\voucher1\public\tamplate_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEEF9D03-DFA2-42E1-B4F4-F01067958B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5767467-9EAF-4E85-B575-75F1A5884B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCDF4430-C9EB-4118-AE8B-51A4AC6386B0}"/>
+    <workbookView xWindow="3165" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{FCDF4430-C9EB-4118-AE8B-51A4AC6386B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -136,6 +136,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,7 +457,7 @@
   <cols>
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -500,7 +502,7 @@
       <c r="B2" s="3">
         <v>45331.946527777778</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2">
@@ -529,7 +531,7 @@
       <c r="B3" s="3">
         <v>45332.004166666666</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2">
